--- a/Data/Tables/__beans__.xlsx
+++ b/Data/Tables/__beans__.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10512"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangyang/Documents/IAAAProject/MiniTemplate/Datas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangyang/Documents/Deliverables/AdPlayerDemo/Data/Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F7B3E2A-2255-E545-BFBF-8E456D11DF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1722938-04C4-A04C-A4FB-EC48C9672362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11860" yWindow="-14960" windowWidth="29260" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="300" yWindow="6320" windowWidth="29260" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -58,6 +58,9 @@
     <t>type</t>
   </si>
   <si>
+    <t>variants</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>字段名</t>
   </si>
   <si>
+    <t>字段别名</t>
+  </si>
+  <si>
     <t>类型</t>
   </si>
   <si>
@@ -79,56 +85,52 @@
     <t>注释</t>
   </si>
   <si>
-    <t>alias</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>字段别名</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>variants</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>字段变体</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card.CardType</t>
+  </si>
+  <si>
+    <t>卡牌类型</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>卡牌等级</t>
   </si>
   <si>
     <t>string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>tileType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>GridTileElement</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>GridTileType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>类型</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>路径</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>des</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>描述</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源路径</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card.CardElement</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>level</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>AssetPath</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -140,37 +142,20 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <family val="4"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <family val="4"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -178,7 +163,19 @@
       <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -191,13 +188,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -228,20 +223,20 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="差" xfId="2" builtinId="27"/>
+    <cellStyle name="差" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="好" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -300,73 +295,13 @@
     <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -378,23 +313,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -404,23 +339,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -428,26 +363,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -482,17 +414,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -514,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="4" width="20.6640625" customWidth="1"/>
@@ -570,7 +502,7 @@
         <v>10</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="L2" t="s">
         <v>11</v>
@@ -585,80 +517,90 @@
         <v>8</v>
       </c>
       <c r="P2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="21.25" customHeight="1">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" t="s">
-        <v>17</v>
-      </c>
-      <c r="N3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="22.75" customHeight="1">
+      <c r="J5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="17" customHeight="1">
-      <c r="J5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="J7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>31</v>
+      <c r="L7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>